--- a/result/Table202512.xlsx
+++ b/result/Table202512.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I15" t="n">
         <v>16.39</v>
       </c>
       <c r="J15" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.23</v>
+        <v>-39.48</v>
       </c>
       <c r="L15" t="n">
-        <v>-39231.24</v>
+        <v>-39475.29</v>
       </c>
     </row>
     <row r="16">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1355,19 +1355,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I19" t="n">
         <v>11.34</v>
       </c>
       <c r="J19" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="K19" t="n">
-        <v>-59.35</v>
+        <v>-59.08</v>
       </c>
       <c r="L19" t="n">
-        <v>-59347.44</v>
+        <v>-59082.89</v>
       </c>
     </row>
     <row r="20">

--- a/result/Table202512.xlsx
+++ b/result/Table202512.xlsx
@@ -566,24 +566,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I3" t="n">
         <v>15.04</v>
       </c>
       <c r="J3" t="n">
-        <v>17.43</v>
+        <v>17.52</v>
       </c>
       <c r="K3" t="n">
-        <v>15.89</v>
+        <v>16.49</v>
       </c>
       <c r="L3" t="n">
-        <v>15890.96</v>
+        <v>16489.36</v>
       </c>
     </row>
     <row r="4">
@@ -762,24 +762,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>14.01</v>
       </c>
       <c r="J7" t="n">
-        <v>15.73</v>
+        <v>14.96</v>
       </c>
       <c r="K7" t="n">
-        <v>12.28</v>
+        <v>6.78</v>
       </c>
       <c r="L7" t="n">
-        <v>12276.95</v>
+        <v>6780.87</v>
       </c>
     </row>
     <row r="8">
@@ -1446,24 +1446,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
         <v>11.28</v>
       </c>
       <c r="J21" t="n">
-        <v>14.02</v>
+        <v>16.06</v>
       </c>
       <c r="K21" t="n">
-        <v>24.29</v>
+        <v>42.38</v>
       </c>
       <c r="L21" t="n">
-        <v>24290.78</v>
+        <v>42375.89</v>
       </c>
     </row>
     <row r="22">
@@ -1642,24 +1642,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
         <v>20.72</v>
       </c>
       <c r="J25" t="n">
-        <v>22.37</v>
+        <v>20.13</v>
       </c>
       <c r="K25" t="n">
-        <v>7.96</v>
+        <v>-2.85</v>
       </c>
       <c r="L25" t="n">
-        <v>7963.32</v>
+        <v>-2847.49</v>
       </c>
     </row>
     <row r="26">
@@ -1930,24 +1930,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
         <v>14.86</v>
       </c>
       <c r="J31" t="n">
-        <v>13.4</v>
+        <v>12.69</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.83</v>
+        <v>-14.6</v>
       </c>
       <c r="L31" t="n">
-        <v>-9825.030000000001</v>
+        <v>-14602.96</v>
       </c>
     </row>
     <row r="32">
@@ -1976,24 +1976,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" t="n">
         <v>98.67</v>
       </c>
       <c r="J32" t="n">
-        <v>109.02</v>
+        <v>104.09</v>
       </c>
       <c r="K32" t="n">
-        <v>10.49</v>
+        <v>5.49</v>
       </c>
       <c r="L32" t="n">
-        <v>10489.51</v>
+        <v>5493.06</v>
       </c>
     </row>
     <row r="33">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>17.46</v>
       </c>
       <c r="J33" t="n">
-        <v>16.33</v>
+        <v>14.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.47</v>
+        <v>-14.26</v>
       </c>
       <c r="L33" t="n">
-        <v>-6471.94</v>
+        <v>-14261.17</v>
       </c>
     </row>
     <row r="34">
@@ -2214,24 +2214,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
         <v>28.81</v>
       </c>
       <c r="J37" t="n">
-        <v>26.11</v>
+        <v>25.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.369999999999999</v>
+        <v>-13.12</v>
       </c>
       <c r="L37" t="n">
-        <v>-9371.75</v>
+        <v>-13120.44</v>
       </c>
     </row>
     <row r="38">
@@ -2260,24 +2260,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
         <v>23.16</v>
       </c>
       <c r="J38" t="n">
-        <v>24.9</v>
+        <v>23.74</v>
       </c>
       <c r="K38" t="n">
-        <v>7.51</v>
+        <v>2.5</v>
       </c>
       <c r="L38" t="n">
-        <v>7512.95</v>
+        <v>2504.32</v>
       </c>
     </row>
     <row r="39">

--- a/result/Table202512.xlsx
+++ b/result/Table202512.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I15" t="n">
         <v>16.39</v>
       </c>
       <c r="J15" t="n">
-        <v>9.92</v>
+        <v>9.6</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.48</v>
+        <v>-41.43</v>
       </c>
       <c r="L15" t="n">
-        <v>-39475.29</v>
+        <v>-41427.7</v>
       </c>
     </row>
     <row r="16">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1355,19 +1355,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I19" t="n">
         <v>11.34</v>
       </c>
       <c r="J19" t="n">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>-59.08</v>
+        <v>-61.2</v>
       </c>
       <c r="L19" t="n">
-        <v>-59082.89</v>
+        <v>-61199.29</v>
       </c>
     </row>
     <row r="20">

--- a/result/Table202512.xlsx
+++ b/result/Table202512.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I15" t="n">
         <v>16.39</v>
       </c>
       <c r="J15" t="n">
-        <v>9.6</v>
+        <v>9.31</v>
       </c>
       <c r="K15" t="n">
-        <v>-41.43</v>
+        <v>-43.2</v>
       </c>
       <c r="L15" t="n">
-        <v>-41427.7</v>
+        <v>-43197.07</v>
       </c>
     </row>
     <row r="16">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1355,19 +1355,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I19" t="n">
         <v>11.34</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="K19" t="n">
-        <v>-61.2</v>
+        <v>-62.26</v>
       </c>
       <c r="L19" t="n">
-        <v>-61199.29</v>
+        <v>-62257.5</v>
       </c>
     </row>
     <row r="20">

--- a/result/Table202512.xlsx
+++ b/result/Table202512.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I15" t="n">
         <v>16.39</v>
       </c>
       <c r="J15" t="n">
-        <v>9.31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-43.2</v>
+        <v>-43.87</v>
       </c>
       <c r="L15" t="n">
-        <v>-43197.07</v>
+        <v>-43868.21</v>
       </c>
     </row>
     <row r="16">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I19" t="n">
         <v>11.34</v>
